--- a/log_analysis/triage_tool/dist/error_db.xlsx
+++ b/log_analysis/triage_tool/dist/error_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -492,6 +492,110 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UVM_FATAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DRV</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[TIMEOUT] AXI write response timeout: addr=0x0000_</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>超时</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>axi_driver.sv</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DUT Bug</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>增加延时</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>tc_sanity</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>melo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UVM_FATAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DRV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TIMEOUT] AXI write response timeout: addr=0x0000_</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dut死锁</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>axi_driver.sv</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DUT Bug</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>设计修改代码</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>tc_perf_test</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>melo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log_analysis/triage_tool/dist/error_db.xlsx
+++ b/log_analysis/triage_tool/dist/error_db.xlsx
@@ -2,32 +2,41 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误知识库" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E74B5"/>
+        <fgColor rgb="FF2E74B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,7 +71,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,14 +435,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -598,5 +605,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>